--- a/Backend/users.xlsx
+++ b/Backend/users.xlsx
@@ -1,41 +1,71 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pathr\hakethon\AgriConnect\Backend\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C83E582-C0C9-402E-B1F2-5CDB52000B8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="13">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>createdAt</t>
+  </si>
+  <si>
+    <t>nagne sachin</t>
+  </si>
+  <si>
+    <t>nagnesachin1@gmail.com</t>
+  </si>
+  <si>
+    <t>$2a$10$eGjzeB.KVkvhRTnfCj1BJuScSkD4egilxPLLRHEBbDE.EpVFey/96</t>
+  </si>
+  <si>
+    <t>farmer</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2026-05-10T09:09:43.772Z</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +95,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,58 +434,1020 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G194"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>email</v>
-      </c>
-      <c r="D1" t="str">
-        <v>password</v>
-      </c>
-      <c r="E1" t="str">
-        <v>type</v>
-      </c>
-      <c r="F1" t="str">
-        <v>phone</v>
-      </c>
-      <c r="G1" t="str">
-        <v>createdAt</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1778404183772</v>
       </c>
-      <c r="B2" t="str">
-        <v>nagne sachin</v>
-      </c>
-      <c r="C2" t="str">
-        <v>nagnesachin1@gmail.com</v>
-      </c>
-      <c r="D2" t="str">
-        <v>$2a$10$eGjzeB.KVkvhRTnfCj1BJuScSkD4egilxPLLRHEBbDE.EpVFey/96</v>
-      </c>
-      <c r="E2" t="str">
-        <v>farmer</v>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v>2026-05-10T09:09:43.772Z</v>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F34" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F42" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F44" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F49" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F50" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F51" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F53" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F54" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F55" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F56" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F57" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F58" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F59" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F60" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F61" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F62" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F63" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F64" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F65" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F66" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F67" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F68" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F69" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F70" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F71" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F72" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F73" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F74" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F75" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F76" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F77" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F78" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F79" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F80" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F81" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F82" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F83" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F84" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F85" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F86" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F87" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F88" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F89" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F90" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F91" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F92" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F93" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="94" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F94" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F95" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F96" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F97" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="98" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F98" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F99" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F100" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F101" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F102" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="103" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F103" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F104" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="105" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F105" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="106" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F106" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="107" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F107" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F108" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="109" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F109" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F110" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F111" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="112" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F112" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="113" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F113" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="114" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F114" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="115" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F115" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="116" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F116" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="117" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F117" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="118" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F118" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F119" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="120" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F120" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F121" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F122" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="123" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F123" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F124" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F125" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F126" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F127" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F128" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="129" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F129" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="130" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F130" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="131" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F131" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F132" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="133" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F133" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="134" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F134" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="135" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F135" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="136" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F136" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F137" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F138" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="139" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F139" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F140" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="141" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F141" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F142" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F143" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F144" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="145" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F145" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F146" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="147" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F147" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F148" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F149" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="150" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F150" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F151" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="152" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F152" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="153" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F153" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F154" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="155" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F155" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="156" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F156" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="157" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F157" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="158" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F158" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="159" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F159" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="160" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F160" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="161" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F161" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F162" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="163" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F163" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="164" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F164" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F165" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="166" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F166" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="167" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F167" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="168" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F168" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="169" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F169" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="170" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F170" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="171" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F171" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="172" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F172" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="173" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F173" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="174" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F174" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="175" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F175" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="176" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F176" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="177" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F177" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="178" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F178" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="179" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F179" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="180" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F180" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="181" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F181" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="182" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F182" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="183" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F183" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="184" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F184" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="185" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F185" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="186" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F186" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="187" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F187" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="188" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F188" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="189" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F189" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="190" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F190" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="191" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F191" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="192" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F192" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="193" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F193" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="194" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F194" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError sqref="A1:G2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>